--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-13.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-13.xlsx
@@ -474,751 +474,751 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5583988742103</v>
+        <v>5583921459700</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rayane</t>
+          <t>Waldir</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rayane Ferreira de Queiroz</t>
+          <t>Waldir Martins de Araujo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583988728901</v>
+        <v>5583988958236</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Claudemir</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonas Pereira da Silva</t>
+          <t>Claudemir Neves Pereira</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583999133552</v>
+        <v>5583998567176</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Andre da Silva Lira</t>
+          <t>Residencial Multifamiliar Isabelly Mirante</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5521966523866</v>
+        <v>5583991091106</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington Santana Maciel</t>
+          <t>Jose Fernandes da Silva</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583988553607</v>
+        <v>5583987767134</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luiz Mendes de Pontes Neto</t>
+          <t>Joao Batista Fontes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583988886028</v>
+        <v>5583991982825</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edme</t>
+          <t>Marciel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Edme Batista da Silva</t>
+          <t>Marciel Ancelmo de Farias</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583999497619</v>
+        <v>5583996300669</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rikelmen</t>
+          <t>Laercio</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rikelmen Viegas de Lima</t>
+          <t>Laercio de Melo Machado</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583994210061</v>
+        <v>5583988716802</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gabriele</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gabriele Tais Barbosa Nobrega</t>
+          <t>Jose Bezerra Leite Neto</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583981625744</v>
+        <v>5583988742103</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Franciley</t>
+          <t>Rayane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Franciley Rodrigues Ferreira</t>
+          <t>Rayane Ferreira de Queiroz</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583981589161</v>
+        <v>5583988728901</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Armando</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Armando Silva Antino</t>
+          <t>Jonas Pereira da Silva</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583996067984</v>
+        <v>5583999133552</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paulo Sergio Rodrigues Silva</t>
+          <t>Andre da Silva Lira</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583996096307</v>
+        <v>5521966523866</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maria Marcolina Lima Cardoso</t>
+          <t>Washington Santana Maciel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583988097345</v>
+        <v>5583988553607</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Luiz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Antonio Marcos Fagundes Nascimento</t>
+          <t>Luiz Mendes de Pontes Neto</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583991803318</v>
+        <v>5583988886028</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Edme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ivan Carlos Rosa de Jesus</t>
+          <t>Edme Batista da Silva</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583996634391</v>
+        <v>5583999497619</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Rikelmen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thiago Rodrigues Medeiros</t>
+          <t>Rikelmen Viegas de Lima</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>5583996569611</v>
+        <v>5583994210061</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Romulo</t>
+          <t>Gabriele</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romulo Alves do Nascimento</t>
+          <t>Gabriele Tais Barbosa Nobrega</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>5583965500146</v>
+        <v>5583981625744</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Azianna</t>
+          <t>Franciley</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azianna Maciel Donato</t>
+          <t>Franciley Rodrigues Ferreira</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>5583987447129</v>
+        <v>5583981589161</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Armando</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ana Claudia Rodrigues</t>
+          <t>Armando Silva Antino</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>5583988170547</v>
+        <v>5583996067984</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Almir</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Almir Batista de Souza Junior</t>
+          <t>Paulo Sergio Rodrigues Silva</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="3">
       <c r="A21" s="4" t="n">
-        <v>5583999815304</v>
+        <v>5583996096307</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Paulo Vanberto Patricio de Aquino</t>
+          <t>Maria Marcolina Lima Cardoso</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="3">
       <c r="A22" s="4" t="n">
-        <v>5583986184717</v>
+        <v>5583988097345</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jarbas</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jarbas Bernardo da Silva</t>
+          <t>Antonio Marcos Fagundes Nascimento</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="3">
       <c r="A23" s="4" t="n">
-        <v>5583987083292</v>
+        <v>5583991803318</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Davi</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davi Paes da Silva</t>
+          <t>Ivan Carlos Rosa de Jesus</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="3">
       <c r="A24" s="4" t="n">
-        <v>5583986761853</v>
+        <v>5583996634391</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Afunfin</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Afunfin</t>
+          <t>Thiago Rodrigues Medeiros</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="3">
       <c r="A25" s="4" t="n">
-        <v>5583996399447</v>
+        <v>5583996569611</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paulo</t>
+          <t>Romulo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paulo Henrique da Silva Barros</t>
+          <t>Romulo Alves do Nascimento</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="3">
       <c r="A26" s="4" t="n">
-        <v>5583987561813</v>
+        <v>5583965500146</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Everaldo</t>
+          <t>Azianna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Everaldo Soares de Oliveira Junior</t>
+          <t>Azianna Maciel Donato</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="3">
       <c r="A27" s="4" t="n">
-        <v>5583998899519</v>
+        <v>5583987447129</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jefferson</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jefferson Rodrigues</t>
+          <t>Ana Claudia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="3">
       <c r="A28" s="4" t="n">
-        <v>5584998271370</v>
+        <v>5583988170547</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thaisa</t>
+          <t>Almir</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thaisa Rafaela Costa dos Santos</t>
+          <t>Almir Batista de Souza Junior</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="3">
       <c r="A29" s="4" t="n">
-        <v>5583991439486</v>
+        <v>5583999815304</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Joel</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Joel Jose da Silva</t>
+          <t>Paulo Vanberto Patricio de Aquino</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="3">
       <c r="A30" s="4" t="n">
-        <v>5583988902850</v>
+        <v>5583986184717</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amarildo</t>
+          <t>Jarbas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Amarildo Francisco Ribeiro</t>
+          <t>Jarbas Bernardo da Silva</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="3">
       <c r="A31" s="4" t="n">
-        <v>5512996214110</v>
+        <v>5583987083292</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marcos</t>
+          <t>Davi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Marcos Vinicius Braz</t>
+          <t>Davi Paes da Silva</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="3">
       <c r="A32" s="4" t="n">
-        <v>5583988742345</v>
+        <v>5583986761853</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ivonne</t>
+          <t>Afunfin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ivonne Pereira da Silva</t>
+          <t>Afunfin</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="3">
       <c r="A33" s="4" t="n">
-        <v>5521964851555</v>
+        <v>5583996399447</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Paulo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Andre Magno Alves Costa</t>
+          <t>Paulo Henrique da Silva Barros</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="3">
       <c r="A34" s="4" t="n">
-        <v>5583987573298</v>
+        <v>5583987561813</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Josenildo</t>
+          <t>Everaldo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Josenildo Calixto da Silva</t>
+          <t>Everaldo Soares de Oliveira Junior</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="3">
       <c r="A35" s="4" t="n">
-        <v>5583996210207</v>
+        <v>5583998899519</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Jefferson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Total Service Electric</t>
+          <t>Jefferson Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="3">
       <c r="A36" s="4" t="n">
-        <v>5583986948426</v>
+        <v>5584998271370</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Thaisa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tiago Araujo da Silva</t>
+          <t>Thaisa Rafaela Costa dos Santos</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="3">
       <c r="A37" s="4" t="n">
-        <v>5583991902311</v>
+        <v>5583991439486</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Residencial Santa Catarina</t>
+          <t>Joel Jose da Silva</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="3">
       <c r="A38" s="4" t="n">
-        <v>5583988542710</v>
+        <v>5583988902850</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vitor</t>
+          <t>Amarildo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vitor Daniel Andrade</t>
+          <t>Amarildo Francisco Ribeiro</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="3">
       <c r="A39" s="4" t="n">
-        <v>5583996122107</v>
+        <v>5512996214110</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Marcos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jose Alves Rodrigues</t>
+          <t>Marcos Vinicius Braz</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="3">
       <c r="A40" s="4" t="n">
-        <v>5583988627400</v>
+        <v>5583988742345</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Walda</t>
+          <t>Ivonne</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Walda Correia</t>
+          <t>Ivonne Pereira da Silva</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="3">
       <c r="A41" s="4" t="n">
-        <v>5583996385408</v>
+        <v>5521964851555</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Elton</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Elton de Sousa Menezes</t>
+          <t>Andre Magno Alves Costa</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="3">
       <c r="A42" s="4" t="n">
-        <v>5583987595707</v>
+        <v>5583987573298</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jonatan</t>
+          <t>Josenildo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jonatan Pascoal da Silva</t>
+          <t>Josenildo Calixto da Silva</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="3">
       <c r="A43" s="4" t="n">
-        <v>5583999246057</v>
+        <v>5583996210207</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sandra Caetano do Couto</t>
+          <t>Total Service Electric</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="3">
       <c r="A44" s="4" t="n">
-        <v>5583988626779</v>
+        <v>5583986948426</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Celio</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Celio Roberto Tavares Santos</t>
+          <t>Tiago Araujo da Silva</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="3">
       <c r="A45" s="4" t="n">
-        <v>5583988019693</v>
+        <v>5583991902311</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Residencial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Renata Rodrigues da Silva</t>
+          <t>Residencial Santa Catarina</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="3">
       <c r="A46" s="4" t="n">
-        <v>5551997787396</v>
+        <v>5583988542710</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cezar</t>
+          <t>Vitor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cezar Lopes</t>
+          <t>Vitor Daniel Andrade</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="3">
       <c r="A47" s="4" t="n">
-        <v>5511994391967</v>
+        <v>5583996122107</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Valmir</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valmir Santos</t>
+          <t>Jose Alves Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="3">
       <c r="A48" s="4" t="n">
-        <v>5583993817338</v>
+        <v>5583988627400</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Walda</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jose Dionisio da Silva</t>
+          <t>Walda Correia</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="3">
       <c r="A49" s="4" t="n">
-        <v>5511952886611</v>
+        <v>5583996385408</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Elton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Renata Silva Branco de Andrade</t>
+          <t>Elton de Sousa Menezes</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="3">
       <c r="A50" s="4" t="n">
-        <v>5583987096594</v>
+        <v>5583987595707</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Arnaldo</t>
+          <t>Jonatan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arnaldo Pereira Alves</t>
+          <t>Jonatan Pascoal da Silva</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="3">
       <c r="A51" s="4" t="n">
-        <v>5583996300462</v>
+        <v>5583999246057</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vanicleide</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vanicleide Deodato dos Santos</t>
+          <t>Sandra Caetano do Couto</t>
         </is>
       </c>
     </row>
